--- a/specs/006-master-plan/SRS_Multichannel_Hub_VN.xlsx
+++ b/specs/006-master-plan/SRS_Multichannel_Hub_VN.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Bia_MucLuc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Tong_Quan_Lo_Trinh" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Vai_Tro_Nguoi_Dung" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Dong_Bo_Don_Etsy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Chuan_Hoa_Du_Lieu_Cu" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Dashboard_Don_Hang" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_Dashboard_Tracking" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_Dashboard_San_Xuat" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_Quy_Trinh_Duyet" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Tracking_Va_Fulfillment" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Tinh_Nang_Mo_Rong" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_Phe_Duyet" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Bia_MucLuc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Tong_Quan_Lo_Trinh" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Vai_Tro_Nguoi_Dung" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Dong_Bo_Don_Etsy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Chuan_Hoa_Du_Lieu_Cu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dashboard_Don_Hang" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Dashboard_Tracking" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Dashboard_San_Xuat" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Quy_Trinh_Duyet" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Tracking_Va_Fulfillment" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_File_Va_Auto_Transition" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Tinh_Nang_Mo_Rong" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Phe_Duyet" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Dong_Bo_Don_Etsy'!$A$4:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_Dong_Bo_Don_Etsy'!$A$4:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Chuan_Hoa_Du_Lieu_Cu'!$A$4:$F$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Dashboard_Don_Hang'!$A$4:$F$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_Dashboard_Tracking'!$A$4:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Dashboard_San_Xuat'!$A$4:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_Dashboard_Tracking'!$A$4:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_Dashboard_San_Xuat'!$A$4:$F$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_Quy_Trinh_Duyet'!$A$4:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_Tracking_Va_Fulfillment'!$A$4:$F$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_Tinh_Nang_Mo_Rong'!$A$4:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_Tracking_Va_Fulfillment'!$A$4:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_File_Va_Auto_Transition'!$A$4:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_Tinh_Nang_Mo_Rong'!$A$4:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -597,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -627,7 +629,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>v2.0 (bản đơn giản hoá cho nghiệp vụ)</t>
+          <t>v2.1 (đã tiếp thu bản red-pen của Owner ngày 2026-04-26)</t>
         </is>
       </c>
     </row>
@@ -639,7 +641,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -705,212 +707,243 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="11" ht="99" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Thay đổi so với bản v2.0 (2026-04-26 — red-pen Owner)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1. Vai trò sửa lại: MP DUYỆT file thiết kế (không tự làm), BA LÀM file thiết kế và đẩy nội bộ, RD check giá MỖI NGÀY.
+2. Trạng thái sản xuất mở rộng từ ~10 lên ~17 sub-state (CHỜ FILE → CHỜ DUYỆT → ĐÃ GỬI PROOF → US-od/Vietnam-od → VN-Dish/[Fix]VN-Dish/VN-Dish NG/... → VN-Packed/VN-Packed 1 → VN-Fulfilled).
+3. Work-center group lại theo kỹ thuật in (paper/fabric/wood/engrave/ceramic-print/ceramic-stamp/heatpress/embroidery/assembly/personalize); admin reassign họ → line theo period.
+4. Thêm Sheet 10 mới: File lifecycle &amp; Auto-transition cho pain points #11/#12/#13/#17/#18.
+5. Thêm REQ-SYN-00 (BLOCKER): Owner ký memo business case Etsy API trước Phase 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>MỤC LỤC</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Nội dung</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>00_Bia_MucLuc</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Bìa &amp; Mục lục</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>01_Tong_Quan_Lo_Trinh</t>
+          <t>00_Bia_MucLuc</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tổng quan &amp; Lộ trình 3 giai đoạn</t>
+          <t>Bìa &amp; Mục lục</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>02_Vai_Tro_Nguoi_Dung</t>
+          <t>01_Tong_Quan_Lo_Trinh</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Ai dùng hệ thống (các phòng ban)</t>
+          <t>Tổng quan &amp; Lộ trình 3 giai đoạn</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>03_Dong_Bo_Don_Etsy</t>
+          <t>02_Vai_Tro_Nguoi_Dung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Đồng bộ đơn từ Etsy (qua API)</t>
+          <t>Ai dùng hệ thống (các phòng ban)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>04_Chuan_Hoa_Du_Lieu_Cu</t>
+          <t>03_Dong_Bo_Don_Etsy</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Chuẩn hoá 17.659 đơn cũ</t>
+          <t>Đồng bộ đơn từ Etsy (qua API)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>05_Dashboard_Don_Hang</t>
+          <t>04_Chuan_Hoa_Du_Lieu_Cu</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Dashboard Đơn hàng (BA + Marketing)</t>
+          <t>Chuẩn hoá 17.659 đơn cũ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>06_Dashboard_Tracking</t>
+          <t>05_Dashboard_Don_Hang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Dashboard Tracking (BA)</t>
+          <t>Dashboard Đơn hàng (BA + Marketing)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>07_Dashboard_San_Xuat</t>
+          <t>06_Dashboard_Tracking</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Dashboard Sản xuất (PD)</t>
+          <t>Dashboard Tracking (BA)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>08_Quy_Trinh_Duyet</t>
+          <t>07_Dashboard_San_Xuat</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Quy trình duyệt (file thiết kế / địa chỉ / ticket)</t>
+          <t>Dashboard Sản xuất (PD)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>09_Tracking_Va_Fulfillment</t>
+          <t>08_Quy_Trinh_Duyet</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Nhập tracking &amp; đẩy đơn sản xuất</t>
+          <t>Quy trình duyệt (file thiết kế / địa chỉ / ticket)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>10_Tinh_Nang_Mo_Rong</t>
+          <t>09_Tracking_Va_Fulfillment</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tính năng mở rộng (giai đoạn sau)</t>
+          <t>Nhập tracking &amp; đẩy đơn sản xuất</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>10_File_Va_Auto_Transition</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>File lifecycle &amp; Auto-transition (NEW v2.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>11_Phe_Duyet</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>11_Tinh_Nang_Mo_Rong</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Tính năng mở rộng (giai đoạn sau)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>12_Phe_Duyet</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Phê duyệt &amp; chữ ký</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="70" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Cách đọc: Mỗi sheet từ 03 đến 10 liệt kê các yêu cầu cụ thể, có cột 'Ưu tiên' và 'Giai đoạn'. Ưu tiên P0 (nền cam) = bắt buộc làm trước; P1 (nền vàng) = rất cần; P2 (nền xanh) = có thể làm sau. Giai đoạn 1/2/3 tương ứng với 3 đợt triển khai — xem chi tiết trong sheet '01_Tong_Quan_Lo_Trinh'.</t>
         </is>
@@ -919,23 +952,24 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A30:C30"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -947,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1260,17 +1294,49 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="74" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>REQ-TRF-09</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Chính sách orphan Gearment khi [Fix]VN-Dish</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Khi MP trigger [Fix]VN-Dish (cập nhật yêu cầu mới của khách sau khi đã thiết kế), draft/quote Gearment cũ phải được cancel hoặc auto-expire để tránh tốn phí storage. Document policy với Gearment trước Phase 0; ghi vào contract.</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Devil's advocate N5 (red-pen)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F12"/>
+  <autoFilter ref="A4:F13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1284,7 +1350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1298,14 +1364,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Tính năng mở rộng (Giai đoạn 2-3)</t>
+          <t>[NEW v2.1] File lifecycle &amp; Auto-transition — Giai đoạn 1-2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Các tính năng làm sau MVP: kiểm soát giá, tồn kho NVL, catalog, scan barcode, Amazon, Website.</t>
+          <t>Các yêu cầu mới sinh từ red-pen của Owner (pain #11, #12, #13, #14, #17, #18): file upload 1 lần - route nhiều nơi, wizard bulk download A4, auto-transition trạng thái khi workorder finish, Customer Message Hub aggregate 19 shop.</t>
         </is>
       </c>
     </row>
@@ -1341,433 +1407,241 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>REQ-EXT-01</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Dashboard Kiểm soát giá (Pricing Audit) cho Sales Audit</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Dashboard riêng 25 cột cho phòng Sales Audit: cột A-F nhập tay, G-T tự lấy từ đơn. Hiển thị cả đơn đa tiền tệ.</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sales Audit (RD)</t>
-        </is>
-      </c>
-      <c r="E5" s="25" t="inlineStr">
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>REQ-FIL-01</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Model `design.file` — 1 upload, route nhiều nơi</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>BA upload file thiết kế MỘT LẦN (lưu GDrive ID). Hệ thống tạo design.file record. KHÔNG re-upload qua Discord ở mỗi handover. Pain #11, #18 (red-pen).</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>MP, BA, PD (red-pen #11, #18)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="67" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>REQ-FIL-02</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Model `design.file.route` — quyền đọc theo recipient</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Mỗi design.file link tới N route: recipient_type (MP/BA/PD/Partner), recipient_id, state (pending → sent → ack), delivery_ts. Audit trail toàn bộ luồng file để giải quyết tình trạng lạc file (#11).</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Phòng BA (red-pen #11)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="73" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>REQ-FIL-03</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Wizard `design.print.batch` — bulk download A4 layout</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>PD tick các file đã duyệt → bấm 'Generate A4 Layout' → Odoo render PDF dàn lên khổ A4 → download. Cache 24h trong ir.attachment, tự xóa sau timeout. Giải quyết pain #12 — PD đỡ phải search Discord, download, sắp Photoshop.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Phòng PD (red-pen #12)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="67" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>REQ-FIL-04</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Discord giữ làm fallback documented</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Discord không bị gỡ ngay khi go-live. Giữ làm fallback documented trong cutover memo, sunset date phải Owner ký. Tránh trường hợp Odoo/GDrive down → PD không có channel handoff (devil's advocate N4).</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Devil's advocate N4 (red-pen)</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="73" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>REQ-AUT-01</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Auto status transition trên `mrp.workorder.button_finish`</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Server action: khi workorder cuối cùng finish → MO x_substate tự advance (vd: producing_dish → packed). KHÔNG dùng base.automation (fragile, khó debug). Giải quyết pain #13 — bộ phận đỡ tự click chuyển trạng thái thủ công.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>MP, BA, PD (red-pen #13)</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>REQ-AUT-02</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] `_update_design_file_route_state()` trên SO confirm</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Khi BA confirm sale.order, hệ thống tự gọi method explicit để update design.file.route (pending → sent) cho các recipient liên quan (MP, PD). Giải quyết pain #13 — auto routing thay vì click tay.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Phòng BA (red-pen #13, #14)</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>REQ-MSG-01</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Customer Message Hub (export-only)</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Cron mỗi giờ pull GET /v3/application/shops/:shop_id/conversations từ Etsy; chỉ lưu summary (shop, buyer_id, subject, last_update, count) vào etsy.customer.message.log. Click → mở Etsy portal. KHÔNG ingest content (Etsy Conversations scope đã bị reject). Giải quyết pain #17 — MP có 1 dashboard tổng hợp 19 shop.</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Phòng Marketing (red-pen #17)</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Giai đoạn 2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="47" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>REQ-EXT-02</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Quy đổi giá về EURO cho các shop USD/VND/CAD</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>Đơn thuộc shop ngoại tệ khác EUR được tự động quy đổi sang EUR theo tỷ giá ngày đặt đơn, hiển thị cột 'Giá tổng (EUR)'.</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sales Audit (RD)</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>Giai đoạn 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>REQ-EXT-03</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Tô màu theo chênh lệch giá bán vs giá catalog</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>So sánh giá bán với giá catalog: đỏ (thấp hơn), vàng (bằng), tím (cao hơn). Sales Audit lọc nhanh đơn bán lệch giá.</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sales Audit (RD)</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
-        <is>
-          <t>Giai đoạn 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>REQ-EXT-04</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Upload tồn kho NVL từ Excel</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>PD upload file Excel tồn kho nguyên vật liệu đầu kỳ, hệ thống tạo tồn kho ban đầu trong kho 'Nguyên vật liệu'.</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>REQ-EXT-05</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Tự trừ NVL khi chuyển 'Đã sản xuất'</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>Khi đơn chuyển 'Đã sản xuất', hệ thống tự trừ NVL tương ứng theo định mức sản phẩm. Tồn kho cập nhật tức thời.</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-06</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Dự báo NVL 1 / 3 / 12 tháng</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Dashboard hiển thị NVL còn đủ dùng cho 1, 3, 12 tháng tới dựa trên tốc độ tiêu thụ + đơn backlog.</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F10" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-07</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Cảnh báo NVL sắp hết (&lt;2 tháng)</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Khi NVL còn đủ dùng dưới 2 tháng, PD Lead nhận thông báo và dashboard tô đỏ.</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F11" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-08</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Catalog Dashboard theo từng sản phẩm</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Click vào 1 sản phẩm mở form tổng hợp: template thiết kế, ảnh mockup, danh sách đơn đã bán.</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>Phòng BA (#7)</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-09</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Lưu template và mockup trên sản phẩm</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Mỗi sản phẩm có 2 trường file: file template gốc và ảnh mockup dùng để preview trong catalog.</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Phòng BA (#7)</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-10</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>Scan sheet barcode riêng cho PD</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>Trang scan đơn giản dành cho PD quét mã vạch liên tục: ô nhập tự focus, enter xác nhận, hiển thị đơn vừa scan và trạng thái.</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>Phòng BA (#11), PD</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F14" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-11</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Scan kết quả đồng bộ về tất cả dashboard</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>Mỗi lần scan cập nhật đồng thời Dashboard Đơn hàng và Dashboard Sản xuất trong vòng 5 giây.</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Phòng BA, PD</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F15" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="53" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-12</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Tích hợp kênh Amazon (đã được PD gắn tag đỏ)</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>Thêm kết nối Amazon Seller Central để lấy đơn và đẩy tracking, tương tự cách làm với Etsy. Đơn Amazon hiện trên Dashboard chung với tag riêng.</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F16" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>REQ-EXT-13</t>
-        </is>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Mở kênh Website Odoo</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>Dùng module Website sẵn có của Odoo để bán trực tiếp; đơn website vào chung Dashboard Đơn hàng.</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Chủ dự án</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>Giai đoạn 3</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F17"/>
+  <autoFilter ref="A4:F11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1776,6 +1650,599 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Tính năng mở rộng (Giai đoạn 2-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Các tính năng làm sau MVP: kiểm soát giá, tồn kho NVL, catalog, scan barcode, Amazon, Website, AI analytics, multi-technique routing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Mã YC</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tên yêu cầu</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Mô tả</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Ai đề xuất</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Ưu tiên</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Giai đoạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-01</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Dashboard Kiểm soát giá (Pricing Audit) cho Sales Audit</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Dashboard riêng 25 cột cho phòng Sales Audit: cột A-F nhập tay, G-T tự lấy từ đơn. Hiển thị cả đơn đa tiền tệ.</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sales Audit (RD)</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="47" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-02</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Quy đổi giá về EURO cho các shop USD/VND/CAD</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Đơn thuộc shop ngoại tệ khác EUR được tự động quy đổi sang EUR theo tỷ giá ngày đặt đơn, hiển thị cột 'Giá tổng (EUR)'.</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sales Audit (RD)</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-03</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Tô màu theo chênh lệch giá bán vs giá catalog</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>So sánh giá bán với giá catalog: đỏ (thấp hơn), vàng (bằng), tím (cao hơn). Sales Audit lọc nhanh đơn bán lệch giá.</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sales Audit (RD)</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="83" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-03b</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Daily auto-flag đơn lệch giá</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>RD check giá MỖI NGÀY (red-pen sửa từ 'thỉnh thoảng' → 'mỗi ngày'). Cron mỗi sáng list đơn vượt threshold lệch giá; gửi RD thông báo + tô màu trên dashboard. Open question: auto-pause đơn lệch giá hay chỉ dashboard read-only? — Owner quyết (devil's advocate N7).</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sales Audit (red-pen)</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-04</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Upload tồn kho NVL từ Excel</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>PD upload file Excel tồn kho nguyên vật liệu đầu kỳ, hệ thống tạo tồn kho ban đầu trong kho 'Nguyên vật liệu'.</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD)</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>REQ-EXT-05</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Tự trừ NVL khi chuyển 'Đã sản xuất'</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Khi đơn chuyển 'Đã sản xuất', hệ thống tự trừ NVL tương ứng theo định mức sản phẩm. Tồn kho cập nhật tức thời.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD)</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-06</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Dự báo NVL 1 / 3 / 12 tháng</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Dashboard hiển thị NVL còn đủ dùng cho 1, 3, 12 tháng tới dựa trên tốc độ tiêu thụ + đơn backlog.</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD)</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-07</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Cảnh báo NVL sắp hết (&lt;2 tháng)</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Khi NVL còn đủ dùng dưới 2 tháng, PD Lead nhận thông báo và dashboard tô đỏ.</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD)</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-08</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Catalog Dashboard theo từng sản phẩm</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Click vào 1 sản phẩm mở form tổng hợp: template thiết kế, ảnh mockup, danh sách đơn đã bán.</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Phòng BA (#7)</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-09</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Lưu template và mockup trên sản phẩm</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Mỗi sản phẩm có 2 trường file: file template gốc và ảnh mockup dùng để preview trong catalog.</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Phòng BA (#7)</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-10</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Scan sheet barcode riêng cho PD</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Trang scan đơn giản dành cho PD quét mã vạch liên tục: ô nhập tự focus, enter xác nhận, hiển thị đơn vừa scan và trạng thái.</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Phòng BA (#11), PD</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-11</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Scan kết quả đồng bộ về tất cả dashboard</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Mỗi lần scan cập nhật đồng thời Dashboard Đơn hàng và Dashboard Sản xuất trong vòng 5 giây.</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Phòng BA, PD</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="53" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-12</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Tích hợp kênh Amazon (đã được PD gắn tag đỏ)</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Thêm kết nối Amazon Seller Central để lấy đơn và đẩy tracking, tương tự cách làm với Etsy. Đơn Amazon hiện trên Dashboard chung với tag riêng.</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD)</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-13</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Mở kênh Website Odoo</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Dùng module Website sẵn có của Odoo để bán trực tiếp; đơn website vào chung Dashboard Đơn hàng.</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Chủ dự án</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="81" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-14</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] AI analytics — schema export contract</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Defer AI analytics build sang Phase 3+. Trong Phase 1 lock schema export cho sale.order, mrp.production, mrp.workorder, design.file.route, partner.sync.log để BI tool (Metabase / Looker) hoặc AI assistant đọc sau. Tránh premature schema design. Pain #19.</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>MP, BA, PD (red-pen #19)</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="68" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>REQ-EXT-15</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Multi-technique routing (sản phẩm hybrid)</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Sản phẩm có 2-3 kỹ thuật (vd đĩa gốm + thêu + khắc) phải đi qua nhiều WC. Quyết: sequential workorders trên 1 MO, hay split MO theo từng kỹ thuật? Test với 1 SKU mẫu trong Phase B. Devil's advocate N6.</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Tech, PD (red-pen)</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F20"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E5:E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"P0,P1,P2"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2006,11 +2473,12 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>• Kết nối Etsy API và tự lấy đơn mới.
+          <t>• Kết nối Etsy API và tự lấy đơn mới (sau khi Owner ký memo business case — REQ-SYN-00).
 • Chuẩn hoá 17.659 đơn cũ (sửa 423 đơn giá 0, gán tiền tệ, gộp khách trùng có BA duyệt).
 • 3 dashboard: Đơn hàng, Tracking, Sản xuất.
 • Duyệt file thiết kế và duyệt đổi địa chỉ.
 • Nhập tracking từ file Excel GKE Logistics.
+• [v2.1] File lifecycle &amp; routing (1 upload, route MP/BA/PD/Partner) + Auto-transition trạng thái + governance reassign work-center.
 ĐIỀU KIỆN KÝ NHẬN: BA Lead ký đối chiếu dữ liệu cũ; các phòng ban chạy Odoo thay thế Google Sheet 1 tháng, sai lệch &lt;1%.</t>
         </is>
       </c>
@@ -2025,8 +2493,9 @@
         <is>
           <t>• Đẩy đơn sang Gearment qua API và nhận tracking về.
 • Hệ thống ticket cho yêu cầu replace/refund (BA duyệt).
-• Dashboard kiểm soát giá (Pricing Audit) với quy đổi EUR.
+• Dashboard kiểm soát giá (Pricing Audit) với quy đổi EUR + auto-flag daily.
 • Xuất lịch sử tin nhắn Etsy ra file Excel.
+• [v2.1] Customer Message Hub (export-only, aggregate 19 shop) + tracking-state hiển thị trên dashboard.
 ĐIỀU KIỆN KÝ NHẬN: đơn Gearment đi live không lỗi 2 tuần liên tiếp; phòng Sales Audit nghiệm thu dashboard.</t>
         </is>
       </c>
@@ -2043,6 +2512,7 @@
 • Catalog Dashboard cho từng sản phẩm (template, mockup, đơn đã bán).
 • Scan sheet barcode cho PD.
 • Mở thêm kênh Amazon và Website.
+• [v2.1] AI analytics — schema export contract cho BI tool / AI assistant; multi-technique routing cho sản phẩm hybrid.
 ĐIỀU KIỆN KÝ NHẬN: quyết định chi tiết đưa ra khi kết thúc Giai đoạn 2, dựa trên feedback thực tế.</t>
         </is>
       </c>
@@ -2131,7 +2601,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Điều phối chính: rà soát đơn khó, duyệt đổi địa chỉ, duyệt ticket replace/refund, đảm bảo chất lượng dữ liệu, đối chiếu với Google Sheet cũ.</t>
+          <t>[v2.1] LÀM file thiết kế và đẩy nội bộ cho MP duyệt; điều phối đơn (US-od / Vietnam-od); cung cấp tracking; duyệt đổi địa chỉ; duyệt ticket replace/refund; đảm bảo chất lượng dữ liệu.</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -2151,12 +2621,12 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Quản lý các store Etsy, push đơn ưu tiên, trả lời khách, gửi yêu cầu đổi địa chỉ, bật/tắt tự động đẩy tracking.</t>
+          <t>[v2.1] Quản lý 19 store Etsy; push đơn ưu tiên; DUYỆT file thiết kế do BA làm; gửi file preview cho khách; xử lý tin nhắn khách; gửi yêu cầu đổi địa chỉ; set US-od / Vietnam-od; bật/tắt auto-push tracking.</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Dashboard Đơn hàng, form chi tiết đơn, popup thông báo.</t>
+          <t>Dashboard Đơn hàng, form chi tiết đơn, popup thông báo, Customer Message Hub.</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2641,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Làm hàng thực tế: in, thêu, khắc, ép nhiệt; scan hàng khi xong, quản tồn kho nguyên vật liệu.</t>
+          <t>[v2.1] Làm hàng thực tế: in giấy/vải/gỗ, khắc gỗ, in/tem gốm, ép nhiệt, thêu, lắp ráp, cá nhân hóa; cập nhật ~17 sub-state qua các bước; scan hàng khi xong; quản tồn kho NVL; bulk-print A4 layout wizard.</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Dashboard Sản xuất, Scan sheet, màn hình tồn kho NVL.</t>
+          <t>Dashboard Sản xuất, Scan sheet, màn hình tồn kho NVL, Bulk-print wizard.</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2656,12 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Phòng Kiểm soát giá (Sales Audit)</t>
+          <t>Phòng Kiểm soát giá (Sales Audit / RD)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Đảm bảo đơn được bán đúng giá chính sách, phát hiện đơn lệch giá, báo cáo đa tiền tệ.</t>
+          <t>[v2.1] Kiểm tra giá bán + giá ship MỖI NGÀY; phát hiện đơn lệch giá; báo cáo đa tiền tệ; báo trên Discord để MP sửa trong ngày.</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -2214,7 +2684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2271,209 +2741,241 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="62" customHeight="1">
+    <row r="5" ht="87" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
+          <t>REQ-SYN-00</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Quyết định business case Etsy API (BLOCKER)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Email auto-feed của hệ thống cũ đã đạt &lt;1% lỗi. Trước khi đầu tư 6-8 tuần cho Spec 005 (OAuth + webhook + rate limit), Owner phải ký memo giải trình lý do: investor narrative? Latency yêu cầu? Scope mới? Nếu không có lý do rõ, defer Spec 005 và giữ email parsing làm baseline.</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Devil's advocate N1 (red-pen)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
           <t>REQ-SYN-01</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Kết nối tài khoản Etsy an toàn</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Chủ shop vào menu Cài đặt, bấm 'Kết nối Etsy' và đăng nhập một lần. Hệ thống nhớ kết nối và tự gia hạn khi gần hết hạn. Admin nhận cảnh báo trước 7 ngày khi phải đăng nhập lại.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Chủ dự án</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>Giai đoạn 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="57" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="57" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>REQ-SYN-02</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Tự động lấy đơn mới từ Etsy mỗi 5 phút</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Hệ thống tự kéo đơn mới hoặc đơn bị sửa từ Etsy về Odoo mỗi 5 phút. Đơn đã có thì không bị tạo trùng. Sau 5 phút, đơn mới trên Etsy xuất hiện trên dashboard.</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Phòng BA, Marketing</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>Giai đoạn 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>REQ-SYN-03</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Không ghi đè dữ liệu do nghiệp vụ nhập</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Khi Etsy báo cập nhật một đơn đã có, hệ thống chỉ cập nhật trạng thái thanh toán/vận chuyển từ Etsy, giữ nguyên note MP, người phụ trách, trạng thái duyệt file đã nhập bởi các phòng ban.</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Phòng BA</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>Giai đoạn 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="51" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>REQ-SYN-04</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Đẩy tracking về Etsy tự động</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Khi BA nhập tracking + đơn vị vận chuyển, hệ thống gửi thông tin này về Etsy trong vòng 5 phút để khách hàng nhìn thấy trên đơn Etsy.</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Phòng BA, Marketing</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>Giai đoạn 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>REQ-SYN-05</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Công tắc bật/tắt tự động đẩy tracking</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Marketing có nút bật/tắt 'Tự động đẩy tracking lên Etsy' theo từng store. Khi tắt, tracking nhập vào nhưng không được gửi tới Etsy.</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Phòng Marketing</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>Giai đoạn 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>REQ-SYN-06</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Xuất lịch sử tin nhắn Etsy</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Marketing chọn khoảng thời gian và bấm 'Xuất tin nhắn', hệ thống tải xuống file Excel chứa tất cả tin nhắn đã nhận để lưu trữ và rà soát.</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Phòng Marketing (#6)</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Giai đoạn 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F10"/>
+  <autoFilter ref="A4:F11"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3041,7 +3543,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
           <t>REQ-ORD-08</t>
@@ -3054,12 +3556,12 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Marketing bấm nút 'Push' trên đơn → đơn được đánh dấu ưu tiên và tô màu đỏ. Lịch sử thao tác ghi lại ai push và khi nào.</t>
+          <t>Marketing bấm nút 'Push' trên đơn → đơn được đánh dấu ưu tiên và tô màu đỏ. Lịch sử thao tác ghi lại ai push và khi nào. [v2.1] Đơn Amazon đặt CÙNG NGÀY với đơn Etsy được auto-set Push (Amazon yêu cầu thời gian ship strict hơn).</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Phòng Marketing (#4)</t>
+          <t>Phòng Marketing (#4), Owner red-pen</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
@@ -3321,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3602,17 +4104,49 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="84" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>REQ-TRK-08</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Hiển thị state tracking (in-transit / delivered / returned)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Hôm nay MP phải mở từng portal carrier để check state tracking trước khi gửi khách. Cần lấy state trực tiếp qua carrier webhook (USPS / UniUni / YunExpress nơi có API), ghi vào stock.picking.x_tracking_state, live update lên Tracking Dashboard qua bus.bus. Pain #16.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Phòng Marketing (red-pen #16)</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>Giai đoạn 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F11"/>
+  <autoFilter ref="A4:F12"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3626,7 +4160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3747,7 +4281,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="73" customHeight="1">
+    <row r="7" ht="115" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
           <t>REQ-PRO-03</t>
@@ -3755,17 +4289,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>12 trạng thái sản xuất có màu</t>
+          <t>[REV v2.1] 17 sub-state sản xuất có màu (mở rộng theo red-pen)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Trạng thái tiếng Việt có màu: Chờ sản xuất / Đã sản xuất / Sản xuất 1 phần / NG-sx lại / Fix đơn / Duyệt sai / SP thêu (hồng) / SP khắc (nâu) / SP ép nhiệt (cam) / SP mới (xanh) / Fulfilled (xanh) / Quá hạn sản xuất (xanh).</t>
+          <t>Sub-state hiện tại của PD: CHỜ FILE / CHỜ DUYỆT / ĐÃ GỬI PROOF / US-od / Vietnam-od / VN-Dish (xanh lá) / VN-Dish NG (đỏ — audit lỗi, cần làm lại) / [Fix]VN-Dish (cam — MP cập nhật yêu cầu mới của khách) / VN-SP mới (xanh dương) / VN-Apron / VN-Handkerchief / Sản xuất 1 phần / VN-Packed / VN-Packed 1 (cần làm rõ semantics — open decision #11) / VN-Fulfilled / Duyệt sai / Quá hạn sản xuất.</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Phòng Sản xuất (PD)</t>
+          <t>Phòng Sản xuất (PD), Owner red-pen</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3779,33 +4313,33 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>REQ-PRO-04</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Danh sách Loại sản phẩm và Option</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>Dropdown Loại sản phẩm: Ceramic dish, Tattoo, Khăn tay, Đĩa gỗ, Thớt gỗ, Chuông gió, Door hanger, Recipe dish, Bandana, Baby Bib, Tạp dề, Túi tote, Mug, Sticker… Dropdown Option: Wave/Heart/Circle square, Recipe Dish A/B/C với các kích thước, Wooden Ring Dish, Size S/M/L… Quản trị có thể bổ sung.</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>Phòng Sản xuất (PD)</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>[REV v2.1] Work-center group theo kỹ thuật in</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Group lại theo kỹ thuật in (thay vì cut/paint/laser): Paper print → TAT (tattoo); Fabric print → APR (apron) + HK-P (khăn in) + TOT (tote); Wood print → DH (door hanger); Wood engrave (WC_ENGRAVE_BH1) → WB + WWC + WD + WVT; Ceramic print (WC_PRINT_BH1) → RD-P; Ceramic stamp → RD-S; Heatpress (WC_HEATPRESS_BH2) → HKF; Embroidery (WC_EMBROIDER_BH2) → HKF; Assembly (WC_ASSEMBLE_BH1) → WCH; Personalize (WC_PERSONALIZE_*) tùy chọn mọi họ. Admin được quyền reassign họ → line theo period.</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Phòng Sản xuất (PD), Owner red-pen</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Giai đoạn 1</t>
         </is>
@@ -3939,17 +4473,49 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="87" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>REQ-PRO-09</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>[NEW v2.1] Audit log + governance reassign work-center</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Khi admin reassign 1 họ sản phẩm sang line khác, hệ thống ghi mrp.routing.assignment.change (ai / khi nào / lý do). MO đang chạy giữ nguyên x_routing_id_at_creation; chỉ MO mới sau ngày đổi mới dùng routing mới. Cấm reassign khi có MO state=progress trong line đó (chống vỡ BoM).</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Devil's advocate N3 (red-pen)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>Giai đoạn 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F12"/>
+  <autoFilter ref="A4:F13"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Giai đoạn 1,Giai đoạn 2,Giai đoạn 3"</formula1>
     </dataValidation>
   </dataValidations>
